--- a/reports/Debug-snowbowl-20260105/For The Week Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260105/For The Week Ending (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -53,15 +53,6 @@
   </si>
   <si>
     <t>account</t>
-  </si>
-  <si>
-    <t>T101</t>
-  </si>
-  <si>
-    <t>T103</t>
-  </si>
-  <si>
-    <t>T121</t>
   </si>
   <si>
     <t>T100</t>
@@ -466,13 +457,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -483,197 +474,143 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2">
-        <v>23041.91</v>
+        <v>41.30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>75780.52</v>
+        <v>8859.30</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2">
-        <v>1343.34</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="2">
-        <v>10278.09</v>
+        <v>698.59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2">
-        <v>107093.70</v>
+        <v>13442.54</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2">
-        <v>14702.30</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2">
-        <v>43427.20</v>
+        <v>8642.78</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2">
-        <v>698.59</v>
+        <v>17424.16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2">
-        <v>14141.13</v>
+        <v>672.60</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2">
-        <v>5.61</v>
+        <v>1383.35</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2">
-        <v>8642.78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2">
-        <v>17424.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="2">
-        <v>672.60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1383.35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="2">
         <v>2558.76</v>
       </c>
     </row>
